--- a/rtos-api-analysis/results/tizenrt_elapsed_time_summary.xlsx
+++ b/rtos-api-analysis/results/tizenrt_elapsed_time_summary.xlsx
@@ -492,34 +492,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5818</v>
+        <v>80236.89440993789</v>
       </c>
       <c r="C2" t="n">
-        <v>44.41221374045801</v>
+        <v>553.3578924823303</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>241.6092162731765</v>
+        <v>2818.757673074009</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2611</v>
+        <v>25893</v>
       </c>
       <c r="H2" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="I2" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/rtos-api-analysis/results/tizenrt_elapsed_time_summary.xlsx
+++ b/rtos-api-analysis/results/tizenrt_elapsed_time_summary.xlsx
@@ -492,34 +492,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80236.89440993789</v>
+        <v>146997.9316770186</v>
       </c>
       <c r="C2" t="n">
-        <v>553.3578924823303</v>
+        <v>973.4962362716466</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2818.757673074009</v>
+        <v>3791.491147856146</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>25893</v>
+        <v>28496</v>
       </c>
       <c r="H2" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I2" t="n">
         <v>162</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
